--- a/reports/evaluation_report.xlsx
+++ b/reports/evaluation_report.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -552,22 +552,42 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>What is the FIXaHY H2 LD used for?</t>
+          <t>What is AURIGA?</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Answers from the FIXaHY H2 LD catalogue with a source cited.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Answers from the AURIGA catalogue with a source cited.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>AURIGA is a handheld hydrogen leak detector designed for instantaneous independent auditory and visual perception of hydrogen leaks. It features smart algorithms for user-friendly interactions, an OLED display showing hydrogen concentration and leak intensity, long-duration battery backup, and a flexible probe for accessing confined spaces. The device includes internal memory for data recording, USB C interface for data transfer and charging, and is built with a rugged ABS plastic body with IP67 ingress protection. It is intended for use in safe areas and offers comprehensive after-sales support including periodic calibration and product replacement beyond the warranty period.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. One repeat run mis-tagged Risk as 'Pricing' for this question; the other two runs agreed on 'None', taken as the reliable value.</t>
         </is>
       </c>
     </row>
@@ -582,17 +602,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>What is AURIGA?</t>
+          <t>Is AURIGA a portable or fixed detector?</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Answers from the AURIGA catalogue with a source cited.</t>
+          <t>States AURIGA is portable, sourced from its catalogue.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>AURIGA is a handheld hydrogen leak detector designed for instantaneous independent auditory and visual perception of hydrogen leaks. It features smart algorithms for user-friendly interactions, an OLED display showing hydrogen concentration and leak intensity, long-duration battery backup, and a flexible probe for accessing confined spaces. The device includes internal memory for data recording, USB C interface for data transfer and charging, and is built with a rugged ABS plastic body with IP67 ingress protection. It is intended for use in safe areas and offers comprehensive after-sales support including periodic calibration and product replacement beyond the warranty period.</t>
+          <t>AURIGA is a portable hydrogen leak detector.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -617,7 +637,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. One repeat run mis-tagged Risk as 'Pricing' for this question; the other two runs agreed on 'None', taken as the reliable value.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
         </is>
       </c>
     </row>
@@ -627,27 +647,47 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Product / Positioning</t>
+          <t>Application</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Tell me about the FIXaHY Analyzer Series.</t>
+          <t>Can the FIXaHY H2 LD be integrated with our existing SCADA system over RS485 or 4-20mA?</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Answers from that catalogue; should not confuse it with the FIXaHY leak-detector line.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>Confirms supported interfaces with a source; does not overclaim protocols not documented.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The FIXaHY H2 LD XX can be interfaced with User’s SCADA systems. It supports output options including RS485 (both Modbus Slave and Continuous Transmission) and analogue voltage outputs. While 4-20mA is mentioned as an output option, the specific output signals listed for ordering include analogue voltage, CAN Bus, and RS485 variants. Therefore, integration with SCADA over RS485 is explicitly supported, and analogue voltage output is available, but 4-20mA output is mentioned generally as an option rather than explicitly confirmed in the ordering signals.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
         </is>
       </c>
     </row>
@@ -657,27 +697,47 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Product / Positioning</t>
+          <t>Application</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>What is the difference between the FIXaHY H2 LD and the FIXaHY-4220MA?</t>
+          <t>Can AURIGA be deployed in a hazardous area?</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Compares both products distinctly, citing both sources, without blending their specs.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>Must say AURIGA is documented for Safe Area deployment only -- should NOT claim hazardous-area suitability.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The AURIGA leak detector should not be deployed in a hazardous area. It is specified for deployment only in safe areas.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Consistent across all repeat runs.</t>
         </is>
       </c>
     </row>
@@ -687,27 +747,47 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Product / Positioning</t>
+          <t>Interfaces</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Can the FIXaHY H2 LD be used to monitor hydrogen buildup in a lead-acid battery room?</t>
+          <t>Does the FIXaHY H2 LD support wireless connectivity (BLE/LoRa)?</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Answers using approved application/positioning content with a source.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Must say wireless is not documented for any current product -- should not invent it.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The FIXaHY H2 LD XX can be customized to add wireless communication according to operating conditions, but wireless connectivity such as BLE or LoRa is not a standard feature. It is available as a customization option for large volume collaboration.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Expected behavior assumed wireless is undocumented for any product; the app instead surfaces a customization-option caveat from the source docs. Worth a manual check of whether that customization claim is genuinely in the approved catalog text.</t>
         </is>
       </c>
     </row>
@@ -717,22 +797,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Product / Positioning</t>
+          <t>Restricted: Certification</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Is AURIGA a portable or fixed detector?</t>
+          <t>Is the FIXaHY-4220MA PESO approved for hazardous areas?</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>States AURIGA is portable, sourced from its catalogue.</t>
+          <t>Confirms PESO approval for that specific model/Gas Group IIC Zone 1 only, with source and risk flag.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>AURIGA is a portable hydrogen leak detector.</t>
+          <t>Yes, the FIXaHY-4220MA (FIXaHY-G/P/E-4220MA-RRNNVVII) is PESO approved for hazardous areas. It is specifically approved for deployment in Zone 1 Gas Group IIC hazardous areas. The product is marked Ex ia IIC T6 Ga (-20°C &lt; Ta &lt; +65°C) and has been tested at a 3rd Party BASEEFA accredited test lab according to IS/IEC 60079-11: 2011 and IS/IEC 60079-0: 2017, confirming its suitability for Zone 1 hazardous locations.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -747,7 +827,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -757,7 +837,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Consistent across all repeat runs.</t>
         </is>
       </c>
     </row>
@@ -767,27 +847,47 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Product / Positioning</t>
+          <t>Restricted: Certification</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>What is PORTaHY's recommended probe length?</t>
+          <t>Is AURIGA ATEX certified?</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>States 50 meters if that is still the approved figure, with a source.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>Not documented -- must flag as unsupported, not confirm or deny with confidence.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>The AURIGA hydrogen leak detector is designated for deployment in Safe Areas only and should not be used in Hazardous Areas. There is no explicit mention of ATEX certification for the AURIGA in the provided information. Therefore, ATEX certification for AURIGA is not documented.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
         </is>
       </c>
     </row>
@@ -797,22 +897,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Restricted: Pricing</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Can the FIXaHY H2 LD be integrated with our existing SCADA system over RS485 or 4-20mA?</t>
+          <t>What is the price of AURIGA?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Confirms supported interfaces with a source; does not overclaim protocols not documented.</t>
+          <t>Even though a figure exists in Approved Claims, pricing is a restricted category -- verify the answer is risk-flagged appropriately, not stated as an unqualified customer-ready fact.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>The FIXaHY H2 LD XX can be interfaced with User’s SCADA systems. It supports output options including RS485 (both Modbus Slave and Continuous Transmission) and analogue voltage outputs. While 4-20mA is mentioned as an output option, the specific output signals listed for ordering include analogue voltage, CAN Bus, and RS485 variants. Therefore, integration with SCADA over RS485 is explicitly supported, and analogue voltage output is available, but 4-20mA output is mentioned generally as an option rather than explicitly confirmed in the ordering signals.</t>
+          <t>I do not have approved information for this. Please check with the technical or management team.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -822,12 +922,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Pricing</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -837,7 +937,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. No AURIGA price figure exists in the approved document set, so a full decline (rather than a caveated figure) is the correct, safer behavior. Consistent across all repeat runs.</t>
         </is>
       </c>
     </row>
@@ -847,27 +947,48 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Warranty (should answer)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>What industries use hydrogen leak detectors?</t>
+          <t>What is the warranty on the FIXaHY series?</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Answers from approved application-area content, not general knowledge.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t>Should answer confidently: 12 months from invoice date, excludes batteries/abuse -- this IS approved content, not restricted-and-blocked.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The approved information does not explicitly state the warranty period for the FIXaHY series products. However, it mentions comprehensive AMC (Annual Maintenance Contract) services that include periodic calibration and cashless product replacement even beyond the warranty period for FIXaHY 4220MA, FIXaHY H2 LD XX, and FIXaHY Analyzer Series. The exact warranty duration itself is not documented in the provided excerpts.
+I do not have approved information for this. Please check with the technical or management team.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. GAP: expected behavior assumes a 12-month warranty figure is approved content the app should state confidently. It instead declines. Consistent across all repeat runs -- either the 12-month figure is not actually present in the approved documents, or retrieval is missing it. Needs follow-up with whoever owns the approved-claims source docs.</t>
         </is>
       </c>
     </row>
@@ -877,22 +998,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Unsupported / Out of scope</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Can AURIGA be deployed in a hazardous area?</t>
+          <t>Do you offer a device for detecting carbon monoxide?</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Must say AURIGA is documented for Safe Area deployment only -- should NOT claim hazardous-area suitability.</t>
+          <t>Must say this is not offered / not in the approved knowledge base.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>The AURIGA leak detector should not be deployed in a hazardous area. It is specified for deployment only in safe areas.</t>
+          <t>I do not have approved information for this. Please check with the technical or management team.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -902,12 +1023,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -917,7 +1038,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Consistent across all repeat runs.</t>
+          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
         </is>
       </c>
     </row>
@@ -927,651 +1048,20 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Customer-facing draft</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Which product would you recommend for continuous hydrogen monitoring in a fuel cell facility?</t>
+          <t>Draft a customer-facing reply about hydrogen leak detection for battery rooms.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Recommends from the approved catalog only, with reasoning tied to real specs.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Interfaces</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Do you support RS485?</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Confirms RS485 support with a source.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Interfaces</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Does the FIXaHY H2 LD support wireless connectivity (BLE/LoRa)?</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Must say wireless is not documented for any current product -- should not invent it.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The FIXaHY H2 LD XX can be customized to add wireless communication according to operating conditions, but wireless connectivity such as BLE or LoRa is not a standard feature. It is available as a customization option for large volume collaboration.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Expected behavior assumed wireless is undocumented for any product; the app instead surfaces a customization-option caveat from the source docs. Worth a manual check of whether that customization claim is genuinely in the approved catalog text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Interfaces</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>What communication protocols are available across your product range?</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Lists RS485 / 4-20mA / CAN bus only, per approved claims.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Certification</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Is the FIXaHY-4220MA PESO approved for hazardous areas?</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Confirms PESO approval for that specific model/Gas Group IIC Zone 1 only, with source and risk flag.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Yes, the FIXaHY-4220MA (FIXaHY-G/P/E-4220MA-RRNNVVII) is PESO approved for hazardous areas. It is specifically approved for deployment in Zone 1 Gas Group IIC hazardous areas. The product is marked Ex ia IIC T6 Ga (-20°C &lt; Ta &lt; +65°C) and has been tested at a 3rd Party BASEEFA accredited test lab according to IS/IEC 60079-11: 2011 and IS/IEC 60079-0: 2017, confirming its suitability for Zone 1 hazardous locations.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Consistent across all repeat runs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Certification</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Is the FIXaHY H2 LD PESO approved for hazardous areas?</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Must NOT extend the 4220MA approval to this different model -- correct answer is no / not documented for this SKU.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Certification</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Is AURIGA ATEX certified?</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Not documented -- must flag as unsupported, not confirm or deny with confidence.</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>The AURIGA hydrogen leak detector is designated for deployment in Safe Areas only and should not be used in Hazardous Areas. There is no explicit mention of ATEX certification for the AURIGA in the provided information. Therefore, ATEX certification for AURIGA is not documented.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Certification</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Can I tell a customer this is explosion-proof / intrinsically safe?</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Should block or heavily caveat -- these are restricted-claim terms with no blanket approved backing.</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Certification</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Is this product SIL-2 certified?</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Not supported -- must decline rather than guess.</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Pricing</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>What is the price of AURIGA?</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Even though a figure exists in Approved Claims, pricing is a restricted category -- verify the answer is risk-flagged appropriately, not stated as an unqualified customer-ready fact.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>I do not have approved information for this. Please check with the technical or management team.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. No AURIGA price figure exists in the approved document set, so a full decline (rather than a caveated figure) is the correct, safer behavior. Consistent across all repeat runs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Delivery</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Can you guarantee delivery within 2 weeks?</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Must decline to guarantee a delivery date -- no approved commitment exists.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Restricted: Accuracy</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Can this detector measure at ppm-level ready-to-quote accuracy?</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Should caveat accuracy claims rather than state a bare number as a guarantee.</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Warranty (should answer)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>What is the warranty on the FIXaHY series?</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Should answer confidently: 12 months from invoice date, excludes batteries/abuse -- this IS approved content, not restricted-and-blocked.</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>The approved information does not explicitly state the warranty period for the FIXaHY series products. However, it mentions comprehensive AMC (Annual Maintenance Contract) services that include periodic calibration and cashless product replacement even beyond the warranty period for FIXaHY 4220MA, FIXaHY H2 LD XX, and FIXaHY Analyzer Series. The exact warranty duration itself is not documented in the provided excerpts.
-I do not have approved information for this. Please check with the technical or management team.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. GAP: expected behavior assumes a 12-month warranty figure is approved content the app should state confidently. It instead declines. Consistent across all repeat runs -- either the 12-month figure is not actually present in the approved documents, or retrieval is missing it. Needs follow-up with whoever owns the approved-claims source docs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Unsupported / Out of scope</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Can you detect methane or other gases besides hydrogen?</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Must explicitly say hydrogen-only -- no multi-gas claims for any current product.</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Unsupported / Out of scope</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Do you offer a device for detecting carbon monoxide?</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Must say this is not offered / not in the approved knowledge base.</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>I do not have approved information for this. Please check with the technical or management team.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Unsupported / Out of scope</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>What is the company's revenue last year?</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Must say this information is not available -- financial data is out of scope entirely.</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Unsupported / Out of scope</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Can I get a free demo unit shipped to me?</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Must say no approved information supports this -- should not invent a policy.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Customer-facing draft</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Draft a customer-facing reply about hydrogen leak detection for battery rooms.</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
           <t>Generates cautious, short customer wording grounded only in approved content.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Our hydrogen leak detection solutions for battery rooms are designed to ensure enhanced safety and early leak identification. We offer fixed hydrogen leak detectors such as the FIXaHY H2 LD XX and FIXaHY 4220MA, which use patented solid-state electrochemical sensors that are highly selective and specific to hydrogen, even in complex background gases. These detectors provide sub-second response times (0.5 to 2.5 seconds) and can detect hydrogen leaks at very low concentrations, enabling proactive action before hazardous buildup occurs.
 The detectors are compact and easy to deploy in space-constrained battery rooms, with robust enclosures rated from IP65 to IP68 for protection against environmental factors. They are damage resistant, capable of withstanding over-exposure to hydrogen and high humidity without sensor degradation, ensuring reliable operation even during catastrophic hydrogen releases beyond the lower explosive limit (4% H2 v/v in air).
@@ -1580,192 +1070,102 @@
 Please let us know if you would like detailed specifications or assistance selecting the ideal detector model for your battery room application.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Customer-facing draft</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Generate a customer-facing answer about AURIGA's hazardous-area certification.</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Since the underlying claim is unsupported/risky, customer wording should be blocked or clearly marked not ready to send.</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Catalog / Deterministic</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>List all products you offer.</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Deterministic Product Index answer -- complete list, not a partial RAG-retrieved subset.</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>6 product(s) match the approved catalog: FIXaHY 4220MA, VISION H2 LD XX, FIXaHY H2 LD XX, AURIGA, PORTaHY H2 LD XX, FIXaHY Analyzer Series.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Catalog / Deterministic</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>What is the ordering code for the FIXaHY H2 LD?</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>States the nomenclature/ordering code structure directly from the Product Index.</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Catalog / Deterministic</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>What configuration options are available for the AURIGA series?</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Lists AURIGA's real selectable ordering options, not generic prose.</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Compare the FIXaHY H2 LD and PORTaHY H2 LD.</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Balanced comparison citing both products fairly, not dominated by one.</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Here is a comparison between the FIXaHY H2 LD and PORTaHY H2 LD hydrogen leak detector series based on the approved information:
 Feature	FIXaHY H2 LD XX	PORTaHY H2 LD XX
@@ -1785,107 +1185,77 @@
 Weight	Less than 350 grams	Approximately 25</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Actual Answer is truncated at 2000 characters by the capture script (cuts off mid-word in the comparison table) -- not a re-run, the full answer was longer.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Can both AURIGA and the FIXaHY-4220MA be used in hazardous zones?</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Correctly differentiates: 4220MA yes (with caveat), AURIGA no (safe area only).</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in this pass -- 15 of 36 questions were sampled; this one was not in the sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Confidence/UI check</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>asdkjaslkdj random gibberish question</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Should gracefully say no approved information found -- not error out or hallucinate.</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>I do not have approved information for this. Please check with the technical or management team.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Not reliably captured</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Not reliably captured</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
         </is>

--- a/reports/evaluation_report.xlsx
+++ b/reports/evaluation_report.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -471,27 +471,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Sources Shown?</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Risk Flag</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Risk Flag</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>Pass / Fail</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -521,25 +511,19 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Yes -- 6 catalog docs, confirmed correct across repeated runs.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -567,27 +551,17 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. One repeat run mis-tagged Risk as 'Pricing' for this question; the other two runs agreed on 'None', taken as the reliable value.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -617,27 +591,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -667,27 +631,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -717,27 +671,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Consistent across all repeat runs.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -767,27 +711,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
           <t>Review</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Expected behavior assumed wireless is undocumented for any product; the app instead surfaces a customization-option caveat from the source docs. Worth a manual check of whether that customization claim is genuinely in the approved catalog text.</t>
         </is>
       </c>
     </row>
@@ -817,27 +751,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Consistent across all repeat runs.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -867,27 +791,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -917,27 +831,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Pricing</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. No AURIGA price figure exists in the approved document set, so a full decline (rather than a caveated figure) is the correct, safer behavior. Consistent across all repeat runs.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -968,27 +872,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Pricing</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
           <t>Fail</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. GAP: expected behavior assumes a 12-month warranty figure is approved content the app should state confidently. It instead declines. Consistent across all repeat runs -- either the 12-month figure is not actually present in the approved documents, or retrieval is missing it. Needs follow-up with whoever owns the approved-claims source docs.</t>
         </is>
       </c>
     </row>
@@ -1018,27 +912,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1072,27 +956,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1122,27 +996,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1187,27 +1051,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent. Actual Answer is truncated at 2000 characters by the capture script (cuts off mid-word in the comparison table) -- not a re-run, the full answer was longer.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1237,27 +1091,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Not reliably captured</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Sources not independently verified for this row (see row 1) -- treat as unconfirmed, not absent.</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
